--- a/Master/9944r00/9944r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/9944r00/9944r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1294,7 +1294,7 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="n">
-        <v>6.23</v>
+        <v>6.242</v>
       </c>
       <c r="B43" s="6" t="n">
         <v>6</v>
@@ -1303,373 +1303,553 @@
         <v>2</v>
       </c>
       <c r="D43" s="7" t="n">
-        <v>4.7476</v>
+        <v>4.7393</v>
       </c>
       <c r="E43" s="7" t="n">
-        <v>-0.3724</v>
+        <v>-2.0403</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>0.006</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="6" t="n">
-        <v>6.13</v>
+        <v>5.243</v>
       </c>
       <c r="B44" s="6" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44" s="7" t="n">
-        <v>4.7653</v>
+        <v>4.7395</v>
       </c>
       <c r="E44" s="7" t="n">
-        <v>-0.3306</v>
+        <v>-2.2219</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>0.0348</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="6" t="n">
-        <v>5.131</v>
+        <v>3.239</v>
       </c>
       <c r="B45" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D45" s="7" t="n">
-        <v>4.8412</v>
+        <v>4.7402</v>
       </c>
       <c r="E45" s="7" t="n">
-        <v>-0.492</v>
+        <v>-1.7802</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>0.0382</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="6" t="n">
-        <v>4.232</v>
+        <v>2.24</v>
       </c>
       <c r="B46" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C46" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D46" s="7" t="n">
-        <v>4.9737</v>
+        <v>4.7421</v>
       </c>
       <c r="E46" s="7" t="n">
-        <v>-0.7245</v>
+        <v>-1.9503</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>0.0005</v>
+        <v>0.0004</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="6" t="n">
-        <v>4.132</v>
+        <v>1.241</v>
       </c>
       <c r="B47" s="6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D47" s="7" t="n">
-        <v>4.9895</v>
+        <v>4.7433</v>
       </c>
       <c r="E47" s="7" t="n">
-        <v>-0.6818</v>
+        <v>-2.1081</v>
       </c>
       <c r="F47" s="7" t="n">
-        <v>0.0186</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="6" t="n">
-        <v>3.133</v>
+        <v>6.23</v>
       </c>
       <c r="B48" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>5.0629</v>
+        <v>4.7476</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>-0.862</v>
+        <v>-0.3724</v>
       </c>
       <c r="F48" s="7" t="n">
-        <v>0.0163</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="6" t="n">
-        <v>2.134</v>
+        <v>6.13</v>
       </c>
       <c r="B49" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C49" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="7" t="n">
-        <v>5.0771</v>
+        <v>4.7653</v>
       </c>
       <c r="E49" s="7" t="n">
-        <v>-0.9484</v>
+        <v>-0.3306</v>
       </c>
       <c r="F49" s="7" t="n">
-        <v>0.0026</v>
+        <v>0.0348</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="6" t="n">
-        <v>1.135</v>
+        <v>5.249</v>
       </c>
       <c r="B50" s="6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C50" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>5.1412</v>
+        <v>4.7676</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>-1.1386</v>
+        <v>-2.9732</v>
       </c>
       <c r="F50" s="7" t="n">
-        <v>0.0024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="6" t="n">
-        <v>6.136</v>
+        <v>6.248</v>
       </c>
       <c r="B51" s="6" t="n">
         <v>6</v>
       </c>
       <c r="C51" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>5.174</v>
+        <v>4.7677</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-1.1101</v>
+        <v>-2.8061</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>0.0217</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="6" t="n">
-        <v>5.237</v>
+        <v>1.247</v>
       </c>
       <c r="B52" s="6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C52" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>5.2014</v>
+        <v>4.7711</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>-1.3009</v>
+        <v>-2.8608</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>0.0056</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="6" t="n">
-        <v>5.137</v>
+        <v>2.246</v>
       </c>
       <c r="B53" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C53" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>5.2248</v>
+        <v>4.7711</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>-1.2965</v>
+        <v>-2.6925</v>
       </c>
       <c r="F53" s="7" t="n">
-        <v>0.0109</v>
+        <v>0.0005999999999999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="n">
-        <v>4.138</v>
+        <v>5.131</v>
       </c>
       <c r="B54" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>5.2808</v>
+        <v>4.8412</v>
       </c>
       <c r="E54" s="7" t="n">
-        <v>-1.5494</v>
+        <v>-0.492</v>
       </c>
       <c r="F54" s="7" t="n">
-        <v>0.0051</v>
+        <v>0.0382</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
-        <v>3.139</v>
+        <v>4.232</v>
       </c>
       <c r="B55" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C55" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>5.2968</v>
+        <v>4.9737</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>-1.7362</v>
+        <v>-0.7245</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>0.0025</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
-        <v>2.14</v>
+        <v>4.132</v>
       </c>
       <c r="B56" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C56" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D56" s="7" t="n">
-        <v>5.3027</v>
+        <v>4.9895</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>-1.9184</v>
+        <v>-0.6818</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>0.0007</v>
+        <v>0.0186</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="6" t="n">
-        <v>1.141</v>
+        <v>3.133</v>
       </c>
       <c r="B57" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>5.3044</v>
+        <v>5.0629</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-2.1027</v>
+        <v>-0.862</v>
       </c>
       <c r="F57" s="7" t="n">
-        <v>0.0004</v>
+        <v>0.0163</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="6" t="n">
-        <v>5.143</v>
+        <v>2.134</v>
       </c>
       <c r="B58" s="6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C58" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D58" s="7" t="n">
-        <v>5.3076</v>
+        <v>5.0771</v>
       </c>
       <c r="E58" s="7" t="n">
-        <v>-2.2017</v>
+        <v>-0.9484</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>0</v>
+        <v>0.0026</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="6" t="n">
-        <v>3.145</v>
+        <v>1.135</v>
       </c>
       <c r="B59" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D59" s="7" t="n">
-        <v>5.3098</v>
+        <v>5.1412</v>
       </c>
       <c r="E59" s="7" t="n">
-        <v>-2.422</v>
+        <v>-1.1386</v>
       </c>
       <c r="F59" s="7" t="n">
-        <v>0.0004</v>
+        <v>0.0024</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="6" t="n">
+        <v>6.136</v>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>5.174</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>-1.1101</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0.0217</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>5.237</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>5.2014</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>-1.3009</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0.0056</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="n">
+        <v>5.137</v>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>5.2248</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>-1.2965</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>0.0109</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>4.138</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>5.2808</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>-1.5494</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>0.0051</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="n">
+        <v>3.139</v>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>5.2968</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>-1.7362</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>0.0025</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>5.3027</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>-1.9184</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>0.0007</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="n">
+        <v>1.141</v>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>5.3044</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>-2.1027</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>5.143</v>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>5.3076</v>
+      </c>
+      <c r="E67" s="7" t="n">
+        <v>-2.2017</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="n">
+        <v>3.145</v>
+      </c>
+      <c r="B68" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C68" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>5.3098</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>-2.422</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>0.0004</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
         <v>4.144</v>
       </c>
-      <c r="B60" s="6" t="n">
+      <c r="B69" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D60" s="7" t="n">
+      <c r="C69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="7" t="n">
         <v>5.3098</v>
       </c>
-      <c r="E60" s="7" t="n">
+      <c r="E69" s="7" t="n">
         <v>-2.2968</v>
       </c>
-      <c r="F60" s="7" t="n">
+      <c r="F69" s="7" t="n">
         <v>0.0009</v>
       </c>
     </row>
-    <row r="62">
-      <c r="E62" s="8" t="inlineStr">
+    <row r="71">
+      <c r="E71" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F62" s="9" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="E63" s="8" t="inlineStr">
+      <c r="F71" s="9" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F63" s="10" t="n">
-        <v>1.2821</v>
+      <c r="F72" s="10" t="n">
+        <v>1.2844</v>
       </c>
     </row>
   </sheetData>
